--- a/03_Entregables-diseño/SI - Ciclo II/1 - SI-SGCSSMA - Sistema de gestión de calidad, seguridad, salud y medio ambiente/Instrumentos de evaluación/16_Lista-de-cotejo.xlsx
+++ b/03_Entregables-diseño/SI - Ciclo II/1 - SI-SGCSSMA - Sistema de gestión de calidad, seguridad, salud y medio ambiente/Instrumentos de evaluación/16_Lista-de-cotejo.xlsx
@@ -734,8 +734,8 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>DESARROLLO TÉCNICO
-Resuelve el problema en su totalidad, utilizando métodos o formas aprendidas en clase</t>
+          <t>COMPRENSIÓN DEL PROBLEMA
+Identifica qué pide el caso y con qué datos cuenta</t>
         </is>
       </c>
       <c r="C10" s="15" t="n"/>
@@ -753,8 +753,8 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>CONCLUSIONES
-La conclusión se desprende del desarrollo y responde a la(s) pregunta(s) del caso</t>
+          <t>DESARROLLO TÉCNICO
+Resuelve el problema en su totalidad, utilizando métodos o formas aprendidas en clase</t>
         </is>
       </c>
       <c r="C11" s="15" t="n"/>
@@ -772,8 +772,8 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>ORGANIZACIÓN DEL PRODUCTO
-El producto está ordenado, tiene claridad y coherencia</t>
+          <t>CONCLUSIONES
+La conclusión se desprende del desarrollo y responde a la(s) pregunta(s) del caso</t>
         </is>
       </c>
       <c r="C12" s="15" t="n"/>
@@ -791,8 +791,8 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>SUSTENTACIÓN ORAL
-los integrantes exponen la parte que les corresponde, con orden y claridad</t>
+          <t>ORGANIZACIÓN Y PRESENTACIÓN DEL PRODUCTO
+El producto está ordenado, tiene claridad y coherencia</t>
         </is>
       </c>
       <c r="C13" s="15" t="n"/>
@@ -810,8 +810,8 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>TIEMPO DE EXPOSICIÓN
-se ajusta al tiempo asignado sin desviaciones</t>
+          <t>SUSTENTACIÓN ORAL
+los integrantes exponen la parte que les corresponde, con orden y claridad, dentro del tiempo asignado</t>
         </is>
       </c>
       <c r="C14" s="15" t="n"/>
